--- a/data/biomass/Cadiz_Biomass_C_cores.xlsx
+++ b/data/biomass/Cadiz_Biomass_C_cores.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Laurent\CONTRATS\2024 REWRITE\Cadiz June 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REWRITE\Field_data\seagrass_carbon_2025\data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75EB8D67-2F9B-4305-AB29-A068587A56B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3555" windowWidth="38640" windowHeight="21240" xr2:uid="{513F2F78-57B9-0945-A99C-4254B20FA0B0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="235">
   <si>
     <t>Core Type</t>
   </si>
@@ -739,12 +738,15 @@
   </si>
   <si>
     <t>Dry mass (g)</t>
+  </si>
+  <si>
+    <t>*removed non-seagrass mass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5">
     <font>
       <sz val="12"/>
@@ -824,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -870,6 +872,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1204,9 +1209,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1DA68DA-A679-4845-8CEF-ED7902CB2011}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
@@ -3018,10 +3023,12 @@
         <v>13.366</v>
       </c>
       <c r="J43" s="16">
-        <f t="shared" si="1"/>
-        <v>1.548</v>
-      </c>
-      <c r="K43" s="9"/>
+        <f>+H43-F43-0.04</f>
+        <v>1.508</v>
+      </c>
+      <c r="K43" s="22" t="s">
+        <v>234</v>
+      </c>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15">
